--- a/ARM Functions/Move Edits/Inverse Room (Move).xlsx
+++ b/ARM Functions/Move Edits/Inverse Room (Move).xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Move Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E2B2C4-10C4-47AC-9670-465CCA468ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022F4154-1AB1-4E57-A2CF-DE3EF2B0B8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="2571" yWindow="2571" windowWidth="24686" windowHeight="12832" activeTab="1" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Original Trick Room" sheetId="12" r:id="rId1"/>
     <sheet name="code " sheetId="13" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="15" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
   <si>
     <t>Address</t>
   </si>
@@ -233,12 +233,6 @@
   </si>
   <si>
     <t>set text 2024</t>
-  </si>
-  <si>
-    <t>000D7038</t>
-  </si>
-  <si>
-    <t>000C6A4C</t>
   </si>
   <si>
     <t>0CD04DE2</t>
@@ -577,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
@@ -599,8 +593,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -1772,8 +1764,8 @@
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="8" t="s">
-        <v>65</v>
+      <c r="A3" s="8">
+        <v>0</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
@@ -1787,7 +1779,7 @@
     <row r="4" spans="1:4">
       <c r="A4" s="8" t="str">
         <f t="shared" ref="A4:A7" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
-        <v>000D703C</v>
+        <v>00000004</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>5</v>
@@ -1800,7 +1792,7 @@
     <row r="5" spans="1:4">
       <c r="A5" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>000D7040</v>
+        <v>00000008</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>7</v>
@@ -1813,7 +1805,7 @@
     <row r="6" spans="1:4">
       <c r="A6" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>000D7044</v>
+        <v>0000000C</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>9</v>
@@ -1825,7 +1817,7 @@
     <row r="7" spans="1:4">
       <c r="A7" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>000D7048</v>
+        <v>00000010</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>4</v>
@@ -1840,8 +1832,8 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="9" t="s">
-        <v>66</v>
+      <c r="A10" s="9">
+        <v>0</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>24</v>
@@ -1853,10 +1845,10 @@
     <row r="11" spans="1:4">
       <c r="A11" s="8" t="str">
         <f t="shared" ref="A11:A58" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
-        <v>000C6A50</v>
+        <v>00000004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>39</v>
@@ -1865,10 +1857,10 @@
     <row r="12" spans="1:4">
       <c r="A12" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A54</v>
+        <v>00000008</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>29</v>
@@ -1877,10 +1869,10 @@
     <row r="13" spans="1:4">
       <c r="A13" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A58</v>
+        <v>0000000C</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>30</v>
@@ -1889,7 +1881,7 @@
     <row r="14" spans="1:4">
       <c r="A14" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A5C</v>
+        <v>00000010</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>12</v>
@@ -1904,10 +1896,10 @@
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A60</v>
+        <v>00000014</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>19</v>
@@ -1917,10 +1909,10 @@
     <row r="16" spans="1:4">
       <c r="A16" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A64</v>
+        <v>00000018</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>31</v>
@@ -1930,298 +1922,297 @@
     <row r="17" spans="1:4">
       <c r="A17" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A68</v>
+        <v>0000001C</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C17" s="16" t="str">
         <f>_xlfn.CONCAT("bne 0x",A56)</f>
-        <v>bne 0x000C6B04</v>
+        <v>bne 0x000000B8</v>
       </c>
       <c r="D17" s="16"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A6C</v>
+        <v>00000020</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C18" s="4" t="str">
         <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A58)-HEX2DEC(A18)-8,"]")</f>
         <v>ldr r1, [pc, #152]</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A70</v>
+        <v>00000024</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A74</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C20" s="21" t="s">
+      <c r="A20" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>00000028</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>114</v>
+      <c r="C20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A78</v>
+        <v>0000002C</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A7C</v>
+        <v>00000030</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6A80</v>
+        <v>00000034</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A84</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="23" t="s">
+      <c r="A24" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>00000038</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="23" t="s">
-        <v>113</v>
+      <c r="D24" s="21" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A88</v>
-      </c>
-      <c r="B25" s="24" t="s">
+      <c r="A25" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>0000003C</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="23"/>
+      <c r="D25" s="21"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A8C</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="23" t="s">
+      <c r="A26" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>00000040</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="23"/>
+      <c r="D26" s="21"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A90</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="23" t="s">
+      <c r="A27" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>00000044</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="23"/>
+      <c r="D27" s="21"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A94</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="23" t="s">
+      <c r="A28" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>00000048</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="23"/>
+      <c r="D28" s="21"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="21" t="str">
+      <c r="A29" s="8" t="str">
         <f>DEC2HEX(HEX2DEC(A28)+4,8)</f>
-        <v>000C6A98</v>
-      </c>
-      <c r="B29" s="22" t="s">
+        <v>0000004C</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>00000050</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="8" t="str">
+        <f>_xlfn.CONCAT("blo 0x",A35)</f>
+        <v>blo 0x00000064</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>00000054</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C31" s="8" t="str">
+        <f>_xlfn.CONCAT("bhi 0x",A43)</f>
+        <v>bhi 0x00000084</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>00000058</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="D29" s="21"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6A9C</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="21" t="str">
-        <f>_xlfn.CONCAT("blo 0x",A35)</f>
-        <v>blo 0x000C6AB0</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6AA0</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C31" s="21" t="str">
-        <f>_xlfn.CONCAT("bhi 0x",A43)</f>
-        <v>bhi 0x000C6AD0</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v>000C6AA4</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AA8</v>
+        <v>0000005C</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AAC</v>
+        <v>00000060</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C34" s="1" t="str">
         <f>_xlfn.CONCAT("b 0x",A45)</f>
-        <v>b 0x000C6AD8</v>
+        <v>b 0x0000008C</v>
       </c>
       <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AB0</v>
+        <v>00000064</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AB4</v>
+        <v>00000068</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AB8</v>
+        <v>0000006C</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C37" s="19" t="s">
         <v>46</v>
@@ -2231,10 +2222,10 @@
     <row r="38" spans="1:4">
       <c r="A38" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6ABC</v>
+        <v>00000070</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C38" s="19" t="s">
         <v>34</v>
@@ -2244,10 +2235,10 @@
     <row r="39" spans="1:4">
       <c r="A39" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AC0</v>
+        <v>00000074</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>35</v>
@@ -2257,25 +2248,25 @@
     <row r="40" spans="1:4">
       <c r="A40" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AC4</v>
+        <v>00000078</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>57</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AC8</v>
+        <v>0000007C</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>36</v>
@@ -2285,10 +2276,10 @@
     <row r="42" spans="1:4">
       <c r="A42" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>000C6ACC</v>
+        <v>00000080</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C42" s="19" t="s">
         <v>47</v>
@@ -2298,7 +2289,7 @@
     <row r="43" spans="1:4">
       <c r="A43" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AD0</v>
+        <v>00000084</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>60</v>
@@ -2313,7 +2304,7 @@
     <row r="44" spans="1:4">
       <c r="A44" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AD4</v>
+        <v>00000088</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>61</v>
@@ -2325,10 +2316,10 @@
     <row r="45" spans="1:4">
       <c r="A45" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AD8</v>
+        <v>0000008C</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>48</v>
@@ -2337,10 +2328,10 @@
     <row r="46" spans="1:4">
       <c r="A46" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6ADC</v>
+        <v>00000090</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>42</v>
@@ -2349,10 +2340,10 @@
     <row r="47" spans="1:4">
       <c r="A47" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AE0</v>
+        <v>00000094</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>56</v>
@@ -2361,10 +2352,10 @@
     <row r="48" spans="1:4">
       <c r="A48" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AE4</v>
+        <v>00000098</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>34</v>
@@ -2373,10 +2364,10 @@
     <row r="49" spans="1:6">
       <c r="A49" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AE8</v>
+        <v>0000009C</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>42</v>
@@ -2385,10 +2376,10 @@
     <row r="50" spans="1:6">
       <c r="A50" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AEC</v>
+        <v>000000A0</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>55</v>
@@ -2397,10 +2388,10 @@
     <row r="51" spans="1:6">
       <c r="A51" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AF0</v>
+        <v>000000A4</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>37</v>
@@ -2409,7 +2400,7 @@
     <row r="52" spans="1:6">
       <c r="A52" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AF4</v>
+        <v>000000A8</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>18</v>
@@ -2421,7 +2412,7 @@
     <row r="53" spans="1:6">
       <c r="A53" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AF8</v>
+        <v>000000AC</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>16</v>
@@ -2433,7 +2424,7 @@
     <row r="54" spans="1:6">
       <c r="A54" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6AFC</v>
+        <v>000000B0</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>25</v>
@@ -2446,10 +2437,10 @@
     <row r="55" spans="1:6">
       <c r="A55" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6B00</v>
+        <v>000000B4</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>15</v>
@@ -2458,10 +2449,10 @@
     <row r="56" spans="1:6">
       <c r="A56" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6B04</v>
+        <v>000000B8</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>37</v>
@@ -2470,7 +2461,7 @@
     <row r="57" spans="1:6">
       <c r="A57" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6B08</v>
+        <v>000000BC</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>26</v>
@@ -2487,13 +2478,13 @@
     <row r="58" spans="1:6">
       <c r="A58" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>000C6B0C</v>
+        <v>000000C0</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2700,47 +2691,47 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2749,7 +2740,7 @@
         <v>00766CC8</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2758,7 +2749,7 @@
         <v>00766CCC</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2767,7 +2758,7 @@
         <v>00766CD0</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2776,7 +2767,7 @@
         <v>00766CD4</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2785,7 +2776,7 @@
         <v>00766CD8</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2794,7 +2785,7 @@
         <v>00766CDC</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2812,7 +2803,7 @@
         <v>00766CE4</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2840,7 +2831,7 @@
         <v>00766CF0</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2849,7 +2840,7 @@
         <v>00766CF4</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2858,7 +2849,7 @@
         <v>00766CF8</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2867,7 +2858,7 @@
         <v>00766CFC</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2876,17 +2867,17 @@
         <v>00766D00</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="D20" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="D21" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
